--- a/ExcelProject/RequestWithdraw.xlsx
+++ b/ExcelProject/RequestWithdraw.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
   <si>
     <t>Execute</t>
   </si>
@@ -55,9 +55,6 @@
     <t>ถอนเงินสำเร็จ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>TC12:02</t>
   </si>
   <si>
@@ -196,7 +193,7 @@
     <t>TC12 : 12  จำนวนเงินในบันชีต้องมากกว่าที่ถอน</t>
   </si>
   <si>
-    <t>TC12 : 13  จำนวนเงินในบันชีต้องน้อยกว่าที่ถอน</t>
+    <t>TC12 : 15  จำนวนเงินในบันชีต้องน้อยกว่าที่ถอน</t>
   </si>
 </sst>
 </file>
@@ -265,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -277,9 +274,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -605,15 +599,15 @@
   <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="18.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="39.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="67.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="30.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="43.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="58.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="55.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -664,12 +658,8 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
@@ -677,11 +667,11 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" s="4">
         <v>6606678082</v>
       </c>
@@ -689,7 +679,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -700,7 +690,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -723,19 +713,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="5">
+        <v>660667808</v>
+      </c>
+      <c r="E5" s="4">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="6">
-        <v>660667808</v>
-      </c>
-      <c r="E5" s="4">
-        <v>100</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -746,19 +736,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>66066780825</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -769,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
@@ -792,19 +782,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="4">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" s="4">
-        <v>100</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -815,19 +805,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4">
+        <v>6606678082</v>
+      </c>
+      <c r="E9" s="4">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E9" s="4">
-        <v>100</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -838,7 +828,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -861,19 +851,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4">
+        <v>6606678082</v>
+      </c>
+      <c r="E11" s="4">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E11" s="4">
-        <v>100</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -884,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>11</v>
@@ -907,7 +897,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>11</v>
@@ -927,10 +917,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
       <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -942,12 +932,10 @@
         <v>99</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
@@ -955,7 +943,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>11</v>
@@ -978,19 +966,19 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="4">
+        <v>6606678082</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -1001,19 +989,19 @@
         <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="4">
+        <v>6606678082</v>
+      </c>
+      <c r="E17" s="4">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E17" s="4">
-        <v>100</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -1024,7 +1012,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>11</v>
@@ -1047,19 +1035,19 @@
         <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4">
+        <v>6606678082</v>
+      </c>
+      <c r="E19" s="4">
+        <v>100</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E19" s="4">
-        <v>100</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -1070,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>11</v>
@@ -1091,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>11</v>
@@ -1112,7 +1100,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>11</v>
@@ -1133,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>11</v>
@@ -1154,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>11</v>
@@ -1175,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>11</v>
@@ -1196,7 +1184,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>11</v>
@@ -1217,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>11</v>
@@ -1238,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>11</v>
@@ -1254,12 +1242,12 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>11</v>
@@ -1275,12 +1263,12 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25">
       <c r="A30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>11</v>
@@ -1296,12 +1284,12 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20.25">
       <c r="A31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>11</v>
@@ -1322,7 +1310,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>11</v>
@@ -1343,7 +1331,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>11</v>
@@ -1364,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>11</v>
@@ -1385,7 +1373,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>11</v>
@@ -1406,7 +1394,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>11</v>
@@ -1426,9 +1414,9 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="8" t="s">
-        <v>59</v>
+      <c r="D37" s="6"/>
+      <c r="E37" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -1439,9 +1427,9 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8" t="s">
-        <v>60</v>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>

--- a/ExcelProject/RequestWithdraw.xlsx
+++ b/ExcelProject/RequestWithdraw.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="42">
   <si>
     <t>Execute</t>
   </si>
@@ -52,7 +52,14 @@
     <t>ธนาคารกรุงเทพ (BBL)</t>
   </si>
   <si>
-    <t>ถอนเงินสำเร็จ</t>
+    <t>ส่งคำขอถอนเงินเรียบร้อยแล้ว ระบบจะดำเนินการตรวจสอบ</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass
+</t>
   </si>
   <si>
     <t>TC12:02</t>
@@ -67,7 +74,7 @@
     <t>TC12:04</t>
   </si>
   <si>
-    <t>กรุณากรอกเป็นตัวเลข 10 หลัก</t>
+    <t>เลขบัญชีต้องเป็นตัวเลข 10 หลักเท่านั้น</t>
   </si>
   <si>
     <t>TC12:05</t>
@@ -85,19 +92,25 @@
     <t>กรุณากรอกเป็นตัวเลขเท่านั้น</t>
   </si>
   <si>
+    <t>กรุณากรอกเลขบัญชีธนาคาร</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>TC12:08</t>
   </si>
   <si>
-    <t>กรุณากรอกเลขบัญชี</t>
-  </si>
-  <si>
     <t>TC12:09</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>TC12:10</t>
   </si>
   <si>
-    <t>กรุณากรอกข้อมูลเป็นตัวเลขจำนวนเต็มบวก หรือทศนิยม 2 ตำแหน่ง</t>
+    <t>จำนวนเงินต้องเป็นตัวเลขจำนวนเต็มบวก</t>
   </si>
   <si>
     <t>TC12:11</t>
@@ -106,9 +119,6 @@
     <t>TC12:12</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>TC12:13</t>
   </si>
   <si>
@@ -124,84 +134,23 @@
     <t>จำนวนเงินถอนต้องไม่เกินเงินคงเหลือปัจจุบัน</t>
   </si>
   <si>
+    <t>จำนวนเงินถอนต้องไม่เกินเงินคงเหลือปัจจุบัน (29702 บาท)</t>
+  </si>
+  <si>
     <t>TC12:16</t>
   </si>
   <si>
-    <t>กรุณากรอกจำนวนที่ต้องการถอน</t>
-  </si>
-  <si>
-    <t>TC12:17</t>
-  </si>
-  <si>
-    <t>TC12:18</t>
-  </si>
-  <si>
-    <t>กรุณาเลือกหมายเหตุ</t>
-  </si>
-  <si>
-    <t>TC12:19</t>
-  </si>
-  <si>
-    <t>TC12:20</t>
-  </si>
-  <si>
-    <t>TC12:21</t>
-  </si>
-  <si>
-    <t>TC12:22</t>
-  </si>
-  <si>
-    <t>TC12:23</t>
-  </si>
-  <si>
-    <t>TC12:24</t>
-  </si>
-  <si>
-    <t>TC12:25</t>
-  </si>
-  <si>
-    <t>TC12:26</t>
-  </si>
-  <si>
-    <t>TC12:27</t>
-  </si>
-  <si>
-    <t>TC12:28</t>
-  </si>
-  <si>
-    <t>TC12:29</t>
-  </si>
-  <si>
-    <t>TC12:30</t>
-  </si>
-  <si>
-    <t>TC12:31</t>
-  </si>
-  <si>
-    <t>TC12:32</t>
-  </si>
-  <si>
-    <t>TC12:33</t>
-  </si>
-  <si>
-    <t>TC12:34</t>
-  </si>
-  <si>
-    <t>TC12:35</t>
-  </si>
-  <si>
-    <t>TC12 : 12  จำนวนเงินในบันชีต้องมากกว่าที่ถอน</t>
-  </si>
-  <si>
-    <t>TC12 : 15  จำนวนเงินในบันชีต้องน้อยกว่าที่ถอน</t>
+    <t>กรุณากรอกจำนวนเงินที่ต้องการถอน</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,8 +170,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="TH SarabunPSK"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,11 +186,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFc00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFf8cbad"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -258,11 +218,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -276,13 +258,34 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -599,15 +602,15 @@
   <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="43.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="58.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="55.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="15" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="30.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="17" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="58.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="55.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -658,19 +661,25 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="4">
         <v>6606678082</v>
@@ -679,18 +688,24 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -704,62 +719,80 @@
       <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>660667808</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>66066780825</v>
       </c>
       <c r="E6" s="4">
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
@@ -773,62 +806,78 @@
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
+      <c r="D8" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E8" s="4">
         <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="4">
-        <v>6606678082</v>
-      </c>
+      <c r="D9" s="7"/>
       <c r="E9" s="4">
         <v>100</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -839,19 +888,25 @@
       <c r="E10" s="4">
         <v>100</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
+      <c r="G10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>11</v>
@@ -859,22 +914,28 @@
       <c r="D11" s="4">
         <v>6606678082</v>
       </c>
-      <c r="E11" s="4">
-        <v>100</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
+      <c r="E11" s="9">
+        <v>100.543</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>11</v>
@@ -885,19 +946,25 @@
       <c r="E12" s="4">
         <v>100</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25">
+      <c r="G12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>11</v>
@@ -908,19 +975,25 @@
       <c r="E13" s="4">
         <v>101</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
+      <c r="G13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -928,22 +1001,28 @@
       <c r="D14" s="4">
         <v>6606678082</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="6">
         <v>99</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
+      <c r="F14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>11</v>
@@ -954,19 +1033,25 @@
       <c r="E15" s="4">
         <v>500</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
+      <c r="G15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>11</v>
@@ -974,22 +1059,28 @@
       <c r="D16" s="4">
         <v>6606678082</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="6">
         <v>1000000</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
+      <c r="F16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>11</v>
@@ -997,444 +1088,250 @@
       <c r="D17" s="4">
         <v>6606678082</v>
       </c>
-      <c r="E17" s="4">
-        <v>100</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
-      <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E18" s="4">
-        <v>100</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25">
-      <c r="A19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E19" s="4">
-        <v>100</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E20" s="4">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25">
-      <c r="A21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E21" s="4">
-        <v>100</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25">
-      <c r="A22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E22" s="4">
-        <v>100</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
-      <c r="A23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E23" s="4">
-        <v>100</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25">
-      <c r="A24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E24" s="4">
-        <v>100</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
-      <c r="A25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E25" s="4">
-        <v>100</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
-      <c r="A26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E26" s="4">
-        <v>100</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
-      <c r="A27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E27" s="4">
-        <v>100</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.25">
-      <c r="A28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E28" s="4">
-        <v>100</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
-      <c r="A29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E29" s="4">
-        <v>100</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25">
-      <c r="A30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E30" s="4">
-        <v>100</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20.25">
-      <c r="A31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E31" s="4">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21.75">
-      <c r="A32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E32" s="4">
-        <v>100</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21.75">
-      <c r="A33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E33" s="4">
-        <v>100</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E34" s="4">
-        <v>100</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E35" s="4">
-        <v>100</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="4">
-        <v>6606678082</v>
-      </c>
-      <c r="E36" s="4">
-        <v>100</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
